--- a/corrected-bank-specimens-for-user/16-acct430-test-data/parsed-excel/acct430 cash book - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/16-acct430-test-data/parsed-excel/acct430 cash book - parsed.xlsx
@@ -431,7 +431,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.922Z</v>
+        <v>2026-07-14T13:50:04.670Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/16-acct430-test-data/parsed-excel/acct430 cash book - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/16-acct430-test-data/parsed-excel/acct430 cash book - parsed.xlsx
@@ -431,7 +431,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:04.670Z</v>
+        <v>2026-07-17T19:29:58.403Z</v>
       </c>
     </row>
     <row r="5">
